--- a/vega_sensitivity.xlsx
+++ b/vega_sensitivity.xlsx
@@ -450,10 +450,10 @@
         <v>0.7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01992355617144511</v>
+        <v>0.01990178083199611</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3325477669358984</v>
+        <v>-0.3284687046844749</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>0.75</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01992969274527018</v>
+        <v>0.01994491648814769</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.401110041964911</v>
+        <v>-0.4085945102567425</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>0.8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01976677622401836</v>
+        <v>0.01980362093974311</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4332668310000483</v>
+        <v>-0.4516508847640984</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>0.85</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01953472872897066</v>
+        <v>0.01953874774951164</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4483202537077484</v>
+        <v>-0.45450175332363</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>0.9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01927018264047076</v>
+        <v>0.01929412879032782</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.4512496512466452</v>
+        <v>-0.4771448330405796</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>0.95</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01899977356493747</v>
+        <v>0.01891447695171979</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4502318179665276</v>
+        <v>-0.3191816878374556</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01872743576218174</v>
+        <v>0.01872367803438827</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -527,10 +527,10 @@
         <v>1.05</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01848779488509169</v>
+        <v>0.01843134537185497</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4060682496570125</v>
+        <v>-0.4890343925551376</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>1.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01824484073751412</v>
+        <v>0.0181444755978417</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.406208261945658</v>
+        <v>-0.4844650427845092</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>1.15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01804164721556407</v>
+        <v>0.01806766086377546</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3840879768346173</v>
+        <v>-0.3658103702317032</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>1.2</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01786075480313831</v>
+        <v>0.0180299991182322</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3637030116129065</v>
+        <v>-0.290108573953867</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>1.25</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01771613618958676</v>
+        <v>0.01765475759873866</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3393382239242929</v>
+        <v>-0.3576328771528496</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +582,10 @@
         <v>1.3</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01759465180612447</v>
+        <v>0.01755852933528851</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3166462470653455</v>
+        <v>-0.3248569519868803</v>
       </c>
     </row>
   </sheetData>
